--- a/Assets/Excel/CardLevelData.xlsx
+++ b/Assets/Excel/CardLevelData.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -49,6 +49,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>unlockLevel</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -79,6 +82,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>玩家解锁卡牌等级</t>
+  </si>
+  <si>
     <t>一号玉砂壶</t>
   </si>
   <si>
@@ -115,13 +121,13 @@
     <t>二号炼器炉</t>
   </si>
   <si>
-    <t>升级后可以提升二号玉砂壶所锻造灵器的收益。</t>
+    <t>升级后可以提升二号炼器炉所锻造灵器的收益。</t>
   </si>
   <si>
     <t>三号炼器炉</t>
   </si>
   <si>
-    <t>升级后可以提升三号玉砂壶所锻造灵器的收益。</t>
+    <t>升级后可以提升三号炼器炉所锻造灵器的收益。</t>
   </si>
   <si>
     <t>灵酬令</t>
@@ -1177,17 +1183,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="3" max="3" width="17.25" customWidth="1"/>
     <col min="4" max="4" width="14.875" customWidth="1"/>
     <col min="5" max="5" width="16.875" customWidth="1"/>
     <col min="6" max="6" width="59.25" customWidth="1"/>
+    <col min="7" max="7" width="22.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1206,325 +1213,376 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1">
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G7" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="G8" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="G9" s="1">
+        <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E10" s="1">
         <v>7</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="G10" s="1">
+        <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>8</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
+      </c>
+      <c r="G11" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1">
         <v>9</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" s="1">
         <v>11</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="G14" s="1">
+        <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>12</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1">
         <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
+      </c>
+      <c r="G15" s="1">
+        <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E16" s="1">
         <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="G16" s="1">
+        <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1">
         <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="G17" s="1">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
